--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/FLORIDA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/FLORIDA_2023.xlsx
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C214">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C347">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C357">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C497">
